--- a/10_Output/2026-10-21-reisekosten-london-coldewey-holding.xlsx
+++ b/10_Output/2026-10-21-reisekosten-london-coldewey-holding.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Saetze 2026" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Abrechnung!$A$1:$I$77</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Abrechnung!$A$1:$I$83</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -29,7 +29,7 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="C25" authorId="0">
+    <comment ref="C32" authorId="0">
       <text>
         <r>
           <rPr>
@@ -42,7 +42,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C26" authorId="0">
+    <comment ref="C33" authorId="0">
       <text>
         <r>
           <rPr>
@@ -54,7 +54,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C27" authorId="0">
+    <comment ref="C34" authorId="0">
       <text>
         <r>
           <rPr>
@@ -66,7 +66,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C28" authorId="0">
+    <comment ref="C35" authorId="0">
       <text>
         <r>
           <rPr>
@@ -78,7 +78,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C44" authorId="0">
+    <comment ref="C51" authorId="0">
       <text>
         <r>
           <rPr>
@@ -91,7 +91,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D15" authorId="0">
+    <comment ref="D21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -99,12 +99,11 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">OFFEN: gefahrene Kilometer hin und zurück eintragen.
-Die Entfernung konnte nicht verlässlich ermittelt werden, deshalb hier kein geschätzter Wert. Tacho oder Routenplaner, Wert dokumentieren.</t>
+          <t xml:space="preserve">35 km einfach laut Angabe Sascha, hin und zurück also 70 km.</t>
         </r>
       </text>
     </comment>
-    <comment ref="F33" authorId="0">
+    <comment ref="F40" authorId="0">
       <text>
         <r>
           <rPr>
@@ -115,6 +114,18 @@
           <t xml:space="preserve">Gestellte Mahlzeit mit „x“ markieren:
 F = Frühstück, M = Mittagessen, A = Abendessen.
 Dazu zählt auch das im Hotelpreis enthaltene Frühstück.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I29" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Hier den tatsächlich gezahlten Betrag eintragen.</t>
         </r>
       </text>
     </comment>
@@ -158,7 +169,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="127">
   <si>
     <t xml:space="preserve">Reisekostenabrechnung</t>
   </si>
@@ -223,6 +234,36 @@
     <t xml:space="preserve">21.10.2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Noch einzutragen — danach rechnet sich alles von selbst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feld</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Was</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Betrag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zelle I29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frankfurt → London → Frankfurt, gezahlter Preis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zelle I51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel London</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Übernachtung 07. auf 08.10., ohne Frühstücksanteil</t>
+  </si>
+  <si>
     <t xml:space="preserve">A · Fahrt mit eigenem Fahrzeug</t>
   </si>
   <si>
@@ -241,9 +282,6 @@
     <t xml:space="preserve">€/km</t>
   </si>
   <si>
-    <t xml:space="preserve">Betrag</t>
-  </si>
-  <si>
     <t xml:space="preserve">07.10.2026</t>
   </si>
   <si>
@@ -265,6 +303,9 @@
     <t xml:space="preserve">Beschreibung</t>
   </si>
   <si>
+    <t xml:space="preserve">Frankfurt → London → Frankfurt</t>
+  </si>
+  <si>
     <t xml:space="preserve">Flughafen-Parken</t>
   </si>
   <si>
@@ -340,9 +381,6 @@
     <t xml:space="preserve">Beleg-Nr.</t>
   </si>
   <si>
-    <t xml:space="preserve">Hotel London</t>
-  </si>
-  <si>
     <t xml:space="preserve">Beleg fehlt</t>
   </si>
   <si>
@@ -400,19 +438,13 @@
     <t xml:space="preserve">Du hast 06. auf 07.10. genannt. Die Kartenumsätze sprechen für 07. auf 08.10.: Abflug Frankfurt „Pier J NonSchengen T3“ am 07.10., Rückflug „WH Smith Heathrow T2“ und Parkhaus-Ausfahrt am 08.10. Die Abrechnung steht auf 07.–08.10. — bitte prüfen.</t>
   </si>
   <si>
-    <t xml:space="preserve">Entfernung Im Zuckergarten 28 → FRA Terminal 3 und zurück fehlt. Block A, gelb markiert. Bei 0,30 €/km sind das je 10 km rund 3 €.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hotel</t>
   </si>
   <si>
-    <t xml:space="preserve">Keine Hotelzahlung im Kontoauszug gefunden. Rechnung nachreichen, Block D.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flug</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kein Flugticket im Kontoauszug gefunden. Falls privat bezahlt, in Block B ergänzen.</t>
+    <t xml:space="preserve">Betrag in Block D eintragen. Im Kontoauszug dieses Kontos ist die Zahlung nicht — Rechnung beilegen. Enthält sie Frühstück, den Anteil herausrechnen und in Block C das „F“ setzen, das kürzt die Pauschale um 13,20 €.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Betrag in Block B eintragen. Hat die Firma direkt gezahlt, gehört er nicht hierher, sondern unten in „abzüglich direkt von der Firma bezahlt“.</t>
   </si>
   <si>
     <t xml:space="preserve">TfL 30,68 €</t>
@@ -599,6 +631,14 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -614,14 +654,6 @@
     <font>
       <b val="true"/>
       <sz val="12"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="9"/>
-      <color rgb="FFC00000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -659,8 +691,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor rgb="FFFCE4E4"/>
+        <fgColor rgb="FFFCE4E4"/>
+        <bgColor rgb="FFE8E8E8"/>
       </patternFill>
     </fill>
     <fill>
@@ -671,13 +703,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1D9"/>
-        <bgColor rgb="FFE8E8E8"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FFFCE4E4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4E4"/>
+        <fgColor rgb="FFD9E1D9"/>
         <bgColor rgb="FFE8E8E8"/>
       </patternFill>
     </fill>
@@ -731,7 +763,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="39">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -764,23 +796,35 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -800,11 +844,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="168" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="168" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -812,39 +860,35 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -856,7 +900,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1128,7 +1172,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
@@ -1288,552 +1332,553 @@
       <c r="B14" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="I14" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="7" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="B15" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I14" s="7" t="s">
+      <c r="C15" s="10" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="10" t="str">
-        <f aca="false">IF($D15="","",IFERROR(INDEX('Saetze 2026'!$C$15:$C$17,MATCH($C15,'Saetze 2026'!$A$15:$A$17,0)),'Saetze 2026'!$C$15))</f>
-        <v/>
-      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
       <c r="I15" s="11" t="str">
-        <f aca="false">IF($D15="","",$D15*$E15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="10" t="str">
-        <f aca="false">IF($D16="","",IFERROR(INDEX('Saetze 2026'!$C$15:$C$17,MATCH($C16,'Saetze 2026'!$A$15:$A$17,0)),'Saetze 2026'!$C$15))</f>
-        <v/>
-      </c>
+        <f aca="false">IF(N(I29)=0,"fehlt","erledigt")</f>
+        <v>fehlt</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
       <c r="H16" s="10"/>
       <c r="I16" s="11" t="str">
-        <f aca="false">IF($D16="","",$D16*$E16)</f>
+        <f aca="false">IF(N(I51)=0,"fehlt","erledigt")</f>
+        <v>fehlt</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+    </row>
+    <row r="20" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <f aca="false">IF($D21="","",IFERROR(INDEX('Saetze 2026'!$C$15:$C$17,MATCH($C21,'Saetze 2026'!$A$15:$A$17,0)),'Saetze 2026'!$C$15))</f>
+        <v>0.3</v>
+      </c>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="15" t="n">
+        <f aca="false">IF($D21="","",$D21*$E21)</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="12"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="14" t="str">
+        <f aca="false">IF($D22="","",IFERROR(INDEX('Saetze 2026'!$C$15:$C$17,MATCH($C22,'Saetze 2026'!$A$15:$A$17,0)),'Saetze 2026'!$C$15))</f>
         <v/>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="10" t="str">
-        <f aca="false">IF($D17="","",IFERROR(INDEX('Saetze 2026'!$C$15:$C$17,MATCH($C17,'Saetze 2026'!$A$15:$A$17,0)),'Saetze 2026'!$C$15))</f>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="15" t="str">
+        <f aca="false">IF($D22="","",$D22*$E22)</f>
         <v/>
       </c>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="11" t="str">
-        <f aca="false">IF($D17="","",$D17*$E17)</f>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="12"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="14" t="str">
+        <f aca="false">IF($D23="","",IFERROR(INDEX('Saetze 2026'!$C$15:$C$17,MATCH($C23,'Saetze 2026'!$A$15:$A$17,0)),'Saetze 2026'!$C$15))</f>
         <v/>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="10" t="str">
-        <f aca="false">IF($D18="","",IFERROR(INDEX('Saetze 2026'!$C$15:$C$17,MATCH($C18,'Saetze 2026'!$A$15:$A$17,0)),'Saetze 2026'!$C$15))</f>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="15" t="str">
+        <f aca="false">IF($D23="","",$D23*$E23)</f>
         <v/>
       </c>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="11" t="str">
-        <f aca="false">IF($D18="","",$D18*$E18)</f>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="12"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="14" t="str">
+        <f aca="false">IF($D24="","",IFERROR(INDEX('Saetze 2026'!$C$15:$C$17,MATCH($C24,'Saetze 2026'!$A$15:$A$17,0)),'Saetze 2026'!$C$15))</f>
         <v/>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="15" t="n">
-        <f aca="false">SUM(I15:I18)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-    </row>
-    <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="17" t="n">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="17" t="n">
-        <v>8.26</v>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="15" t="str">
+        <f aca="false">IF($D24="","",$D24*$E24)</f>
+        <v/>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="18" t="s">
+      <c r="A25" s="16"/>
+      <c r="B25" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>41</v>
-      </c>
+      <c r="C25" s="16"/>
       <c r="D25" s="16"/>
       <c r="E25" s="16"/>
       <c r="F25" s="16"/>
       <c r="G25" s="16"/>
       <c r="H25" s="16"/>
-      <c r="I25" s="17" t="n">
+      <c r="I25" s="18" t="n">
+        <f aca="false">SUM(I21:I24)</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+    </row>
+    <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="20"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="21" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="21" t="n">
+        <v>8.26</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B32" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="21" t="n">
         <v>30.68</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="17" t="n">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="21" t="n">
         <v>3.73</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="17" t="n">
-        <v>3.72</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="17" t="n">
-        <v>2.36</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="17"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="15" t="n">
-        <f aca="false">SUM(I23:I29)</f>
-        <v>134.75</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-    </row>
-    <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B33" s="7" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="G33" s="7" t="s">
+      <c r="B34" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="H33" s="7" t="s">
+      <c r="C34" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="I33" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D34" s="11" t="n">
-        <f aca="false">IF($A34="","",IFERROR(INDEX('Saetze 2026'!$C$5:$F$7,MATCH($B34,'Saetze 2026'!$B$5:$B$7,0),MATCH($C34,'Saetze 2026'!$C$4:$F$4,0)),0))</f>
-        <v>44</v>
-      </c>
-      <c r="E34" s="11" t="n">
-        <f aca="false">IF($A34="","",IFERROR(INDEX('Saetze 2026'!$C$5:$C$7,MATCH($B34,'Saetze 2026'!$B$5:$B$7,0)),0)*(IF(LOWER($F34)="x",'Saetze 2026'!$B$10,0)+IF(LOWER($G34)="x",'Saetze 2026'!$B$11,0)+IF(LOWER($H34)="x",'Saetze 2026'!$B$12,0)))</f>
-        <v>0</v>
-      </c>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
       <c r="F34" s="19"/>
       <c r="G34" s="19"/>
       <c r="H34" s="19"/>
-      <c r="I34" s="11" t="n">
-        <f aca="false">IF($A34="","",MAX(0,$D34-$E34))</f>
-        <v>44</v>
+      <c r="I34" s="21" t="n">
+        <v>3.72</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="8" t="s">
-        <v>37</v>
+      <c r="A35" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="B35" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C35" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D35" s="11" t="n">
-        <f aca="false">IF($A35="","",IFERROR(INDEX('Saetze 2026'!$C$5:$F$7,MATCH($B35,'Saetze 2026'!$B$5:$B$7,0),MATCH($C35,'Saetze 2026'!$C$4:$F$4,0)),0))</f>
-        <v>44</v>
-      </c>
-      <c r="E35" s="11" t="n">
-        <f aca="false">IF($A35="","",IFERROR(INDEX('Saetze 2026'!$C$5:$C$7,MATCH($B35,'Saetze 2026'!$B$5:$B$7,0)),0)*(IF(LOWER($F35)="x",'Saetze 2026'!$B$10,0)+IF(LOWER($G35)="x",'Saetze 2026'!$B$11,0)+IF(LOWER($H35)="x",'Saetze 2026'!$B$12,0)))</f>
-        <v>0</v>
-      </c>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
       <c r="F35" s="19"/>
       <c r="G35" s="19"/>
       <c r="H35" s="19"/>
-      <c r="I35" s="11" t="n">
-        <f aca="false">IF($A35="","",MAX(0,$D35-$E35))</f>
-        <v>44</v>
+      <c r="I35" s="21" t="n">
+        <v>2.36</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="8"/>
+      <c r="A36" s="12"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
-      <c r="D36" s="11" t="str">
-        <f aca="false">IF($A36="","",IFERROR(INDEX('Saetze 2026'!$C$5:$F$7,MATCH($B36,'Saetze 2026'!$B$5:$B$7,0),MATCH($C36,'Saetze 2026'!$C$4:$F$4,0)),0))</f>
-        <v/>
-      </c>
-      <c r="E36" s="11" t="str">
-        <f aca="false">IF($A36="","",IFERROR(INDEX('Saetze 2026'!$C$5:$C$7,MATCH($B36,'Saetze 2026'!$B$5:$B$7,0)),0)*(IF(LOWER($F36)="x",'Saetze 2026'!$B$10,0)+IF(LOWER($G36)="x",'Saetze 2026'!$B$11,0)+IF(LOWER($H36)="x",'Saetze 2026'!$B$12,0)))</f>
-        <v/>
-      </c>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
       <c r="F36" s="19"/>
       <c r="G36" s="19"/>
       <c r="H36" s="19"/>
-      <c r="I36" s="11" t="str">
-        <f aca="false">IF($A36="","",MAX(0,$D36-$E36))</f>
+      <c r="I36" s="21"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="16"/>
+      <c r="B37" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="18" t="n">
+        <f aca="false">SUM(I29:I36)</f>
+        <v>134.75</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+    </row>
+    <row r="40" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D41" s="15" t="n">
+        <f aca="false">IF($A41="","",IFERROR(INDEX('Saetze 2026'!$C$5:$F$7,MATCH($B41,'Saetze 2026'!$B$5:$B$7,0),MATCH($C41,'Saetze 2026'!$C$4:$F$4,0)),0))</f>
+        <v>44</v>
+      </c>
+      <c r="E41" s="15" t="n">
+        <f aca="false">IF($A41="","",IFERROR(INDEX('Saetze 2026'!$C$5:$C$7,MATCH($B41,'Saetze 2026'!$B$5:$B$7,0)),0)*(IF(LOWER($F41)="x",'Saetze 2026'!$B$10,0)+IF(LOWER($G41)="x",'Saetze 2026'!$B$11,0)+IF(LOWER($H41)="x",'Saetze 2026'!$B$12,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="F41" s="23"/>
+      <c r="G41" s="23"/>
+      <c r="H41" s="23"/>
+      <c r="I41" s="15" t="n">
+        <f aca="false">IF($A41="","",MAX(0,$D41-$E41))</f>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D42" s="15" t="n">
+        <f aca="false">IF($A42="","",IFERROR(INDEX('Saetze 2026'!$C$5:$F$7,MATCH($B42,'Saetze 2026'!$B$5:$B$7,0),MATCH($C42,'Saetze 2026'!$C$4:$F$4,0)),0))</f>
+        <v>44</v>
+      </c>
+      <c r="E42" s="15" t="n">
+        <f aca="false">IF($A42="","",IFERROR(INDEX('Saetze 2026'!$C$5:$C$7,MATCH($B42,'Saetze 2026'!$B$5:$B$7,0)),0)*(IF(LOWER($F42)="x",'Saetze 2026'!$B$10,0)+IF(LOWER($G42)="x",'Saetze 2026'!$B$11,0)+IF(LOWER($H42)="x",'Saetze 2026'!$B$12,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="F42" s="23"/>
+      <c r="G42" s="23"/>
+      <c r="H42" s="23"/>
+      <c r="I42" s="15" t="n">
+        <f aca="false">IF($A42="","",MAX(0,$D42-$E42))</f>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="12"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="15" t="str">
+        <f aca="false">IF($A43="","",IFERROR(INDEX('Saetze 2026'!$C$5:$F$7,MATCH($B43,'Saetze 2026'!$B$5:$B$7,0),MATCH($C43,'Saetze 2026'!$C$4:$F$4,0)),0))</f>
         <v/>
       </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="8"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="11" t="str">
-        <f aca="false">IF($A37="","",IFERROR(INDEX('Saetze 2026'!$C$5:$F$7,MATCH($B37,'Saetze 2026'!$B$5:$B$7,0),MATCH($C37,'Saetze 2026'!$C$4:$F$4,0)),0))</f>
+      <c r="E43" s="15" t="str">
+        <f aca="false">IF($A43="","",IFERROR(INDEX('Saetze 2026'!$C$5:$C$7,MATCH($B43,'Saetze 2026'!$B$5:$B$7,0)),0)*(IF(LOWER($F43)="x",'Saetze 2026'!$B$10,0)+IF(LOWER($G43)="x",'Saetze 2026'!$B$11,0)+IF(LOWER($H43)="x",'Saetze 2026'!$B$12,0)))</f>
         <v/>
       </c>
-      <c r="E37" s="11" t="str">
-        <f aca="false">IF($A37="","",IFERROR(INDEX('Saetze 2026'!$C$5:$C$7,MATCH($B37,'Saetze 2026'!$B$5:$B$7,0)),0)*(IF(LOWER($F37)="x",'Saetze 2026'!$B$10,0)+IF(LOWER($G37)="x",'Saetze 2026'!$B$11,0)+IF(LOWER($H37)="x",'Saetze 2026'!$B$12,0)))</f>
+      <c r="F43" s="23"/>
+      <c r="G43" s="23"/>
+      <c r="H43" s="23"/>
+      <c r="I43" s="15" t="str">
+        <f aca="false">IF($A43="","",MAX(0,$D43-$E43))</f>
         <v/>
       </c>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
-      <c r="H37" s="19"/>
-      <c r="I37" s="11" t="str">
-        <f aca="false">IF($A37="","",MAX(0,$D37-$E37))</f>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="12"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="15" t="str">
+        <f aca="false">IF($A44="","",IFERROR(INDEX('Saetze 2026'!$C$5:$F$7,MATCH($B44,'Saetze 2026'!$B$5:$B$7,0),MATCH($C44,'Saetze 2026'!$C$4:$F$4,0)),0))</f>
         <v/>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="8"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="11" t="str">
-        <f aca="false">IF($A38="","",IFERROR(INDEX('Saetze 2026'!$C$5:$F$7,MATCH($B38,'Saetze 2026'!$B$5:$B$7,0),MATCH($C38,'Saetze 2026'!$C$4:$F$4,0)),0))</f>
+      <c r="E44" s="15" t="str">
+        <f aca="false">IF($A44="","",IFERROR(INDEX('Saetze 2026'!$C$5:$C$7,MATCH($B44,'Saetze 2026'!$B$5:$B$7,0)),0)*(IF(LOWER($F44)="x",'Saetze 2026'!$B$10,0)+IF(LOWER($G44)="x",'Saetze 2026'!$B$11,0)+IF(LOWER($H44)="x",'Saetze 2026'!$B$12,0)))</f>
         <v/>
       </c>
-      <c r="E38" s="11" t="str">
-        <f aca="false">IF($A38="","",IFERROR(INDEX('Saetze 2026'!$C$5:$C$7,MATCH($B38,'Saetze 2026'!$B$5:$B$7,0)),0)*(IF(LOWER($F38)="x",'Saetze 2026'!$B$10,0)+IF(LOWER($G38)="x",'Saetze 2026'!$B$11,0)+IF(LOWER($H38)="x",'Saetze 2026'!$B$12,0)))</f>
+      <c r="F44" s="23"/>
+      <c r="G44" s="23"/>
+      <c r="H44" s="23"/>
+      <c r="I44" s="15" t="str">
+        <f aca="false">IF($A44="","",MAX(0,$D44-$E44))</f>
         <v/>
       </c>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="19"/>
-      <c r="I38" s="11" t="str">
-        <f aca="false">IF($A38="","",MAX(0,$D38-$E38))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="8"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="11" t="str">
-        <f aca="false">IF($A39="","",IFERROR(INDEX('Saetze 2026'!$C$5:$F$7,MATCH($B39,'Saetze 2026'!$B$5:$B$7,0),MATCH($C39,'Saetze 2026'!$C$4:$F$4,0)),0))</f>
-        <v/>
-      </c>
-      <c r="E39" s="11" t="str">
-        <f aca="false">IF($A39="","",IFERROR(INDEX('Saetze 2026'!$C$5:$C$7,MATCH($B39,'Saetze 2026'!$B$5:$B$7,0)),0)*(IF(LOWER($F39)="x",'Saetze 2026'!$B$10,0)+IF(LOWER($G39)="x",'Saetze 2026'!$B$11,0)+IF(LOWER($H39)="x",'Saetze 2026'!$B$12,0)))</f>
-        <v/>
-      </c>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="11" t="str">
-        <f aca="false">IF($A39="","",MAX(0,$D39-$E39))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
-      <c r="H40" s="13"/>
-      <c r="I40" s="15" t="n">
-        <f aca="false">SUM(I34:I39)</f>
-        <v>88</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-    </row>
-    <row r="43" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="I43" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="16"/>
-      <c r="G44" s="16"/>
-      <c r="H44" s="16"/>
-      <c r="I44" s="20"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="8"/>
+      <c r="A45" s="12"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
-      <c r="D45" s="16"/>
-      <c r="E45" s="16"/>
-      <c r="F45" s="16"/>
-      <c r="G45" s="16"/>
-      <c r="H45" s="16"/>
-      <c r="I45" s="17"/>
+      <c r="D45" s="15" t="str">
+        <f aca="false">IF($A45="","",IFERROR(INDEX('Saetze 2026'!$C$5:$F$7,MATCH($B45,'Saetze 2026'!$B$5:$B$7,0),MATCH($C45,'Saetze 2026'!$C$4:$F$4,0)),0))</f>
+        <v/>
+      </c>
+      <c r="E45" s="15" t="str">
+        <f aca="false">IF($A45="","",IFERROR(INDEX('Saetze 2026'!$C$5:$C$7,MATCH($B45,'Saetze 2026'!$B$5:$B$7,0)),0)*(IF(LOWER($F45)="x",'Saetze 2026'!$B$10,0)+IF(LOWER($G45)="x",'Saetze 2026'!$B$11,0)+IF(LOWER($H45)="x",'Saetze 2026'!$B$12,0)))</f>
+        <v/>
+      </c>
+      <c r="F45" s="23"/>
+      <c r="G45" s="23"/>
+      <c r="H45" s="23"/>
+      <c r="I45" s="15" t="str">
+        <f aca="false">IF($A45="","",MAX(0,$D45-$E45))</f>
+        <v/>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="8"/>
+      <c r="A46" s="12"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
-      <c r="D46" s="16"/>
-      <c r="E46" s="16"/>
-      <c r="F46" s="16"/>
-      <c r="G46" s="16"/>
-      <c r="H46" s="16"/>
-      <c r="I46" s="17"/>
+      <c r="D46" s="15" t="str">
+        <f aca="false">IF($A46="","",IFERROR(INDEX('Saetze 2026'!$C$5:$F$7,MATCH($B46,'Saetze 2026'!$B$5:$B$7,0),MATCH($C46,'Saetze 2026'!$C$4:$F$4,0)),0))</f>
+        <v/>
+      </c>
+      <c r="E46" s="15" t="str">
+        <f aca="false">IF($A46="","",IFERROR(INDEX('Saetze 2026'!$C$5:$C$7,MATCH($B46,'Saetze 2026'!$B$5:$B$7,0)),0)*(IF(LOWER($F46)="x",'Saetze 2026'!$B$10,0)+IF(LOWER($G46)="x",'Saetze 2026'!$B$11,0)+IF(LOWER($H46)="x",'Saetze 2026'!$B$12,0)))</f>
+        <v/>
+      </c>
+      <c r="F46" s="23"/>
+      <c r="G46" s="23"/>
+      <c r="H46" s="23"/>
+      <c r="I46" s="15" t="str">
+        <f aca="false">IF($A46="","",MAX(0,$D46-$E46))</f>
+        <v/>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C47" s="13"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="13"/>
-      <c r="I47" s="15" t="n">
-        <f aca="false">SUM(I44:I46)</f>
-        <v>0</v>
+      <c r="A47" s="16"/>
+      <c r="B47" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C47" s="16"/>
+      <c r="D47" s="16"/>
+      <c r="E47" s="16"/>
+      <c r="F47" s="16"/>
+      <c r="G47" s="16"/>
+      <c r="H47" s="16"/>
+      <c r="I47" s="18" t="n">
+        <f aca="false">SUM(I41:I46)</f>
+        <v>88</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -1846,293 +1891,256 @@
     </row>
     <row r="50" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="I50" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="8" t="s">
-        <v>64</v>
+      <c r="A51" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D51" s="16"/>
-      <c r="E51" s="16"/>
-      <c r="F51" s="16"/>
-      <c r="G51" s="16"/>
-      <c r="H51" s="16"/>
-      <c r="I51" s="17" t="n">
-        <v>24.23</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="D51" s="19"/>
+      <c r="E51" s="19"/>
+      <c r="F51" s="19"/>
+      <c r="G51" s="19"/>
+      <c r="H51" s="19"/>
+      <c r="I51" s="20"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="8"/>
+      <c r="A52" s="12"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
-      <c r="D52" s="16"/>
-      <c r="E52" s="16"/>
-      <c r="F52" s="16"/>
-      <c r="G52" s="16"/>
-      <c r="H52" s="16"/>
-      <c r="I52" s="17"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="19"/>
+      <c r="F52" s="19"/>
+      <c r="G52" s="19"/>
+      <c r="H52" s="19"/>
+      <c r="I52" s="21"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="8"/>
+      <c r="A53" s="12"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
-      <c r="D53" s="16"/>
-      <c r="E53" s="16"/>
-      <c r="F53" s="16"/>
-      <c r="G53" s="16"/>
-      <c r="H53" s="16"/>
-      <c r="I53" s="17"/>
+      <c r="D53" s="19"/>
+      <c r="E53" s="19"/>
+      <c r="F53" s="19"/>
+      <c r="G53" s="19"/>
+      <c r="H53" s="19"/>
+      <c r="I53" s="21"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="8"/>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
+      <c r="A54" s="16"/>
+      <c r="B54" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C54" s="16"/>
       <c r="D54" s="16"/>
       <c r="E54" s="16"/>
       <c r="F54" s="16"/>
       <c r="G54" s="16"/>
       <c r="H54" s="16"/>
-      <c r="I54" s="17"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C55" s="13"/>
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13"/>
-      <c r="G55" s="13"/>
-      <c r="H55" s="13"/>
-      <c r="I55" s="15" t="n">
-        <f aca="false">SUM(I51:I54)</f>
+      <c r="I54" s="18" t="n">
+        <f aca="false">SUM(I51:I53)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B56" s="6"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="6"/>
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="6"/>
+    </row>
+    <row r="57" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="I57" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D58" s="19"/>
+      <c r="E58" s="19"/>
+      <c r="F58" s="19"/>
+      <c r="G58" s="19"/>
+      <c r="H58" s="19"/>
+      <c r="I58" s="21" t="n">
         <v>24.23</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B57" s="6"/>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
-      <c r="E57" s="6"/>
-      <c r="F57" s="6"/>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="6"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="I58" s="21" t="n">
-        <f aca="false">I19+I30+I40+I47+I55</f>
-        <v>246.98</v>
-      </c>
-    </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="I59" s="17"/>
+      <c r="A59" s="12"/>
+      <c r="B59" s="4"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="19"/>
+      <c r="E59" s="19"/>
+      <c r="F59" s="19"/>
+      <c r="G59" s="19"/>
+      <c r="H59" s="19"/>
+      <c r="I59" s="21"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I60" s="17"/>
-    </row>
-    <row r="61" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="23"/>
-      <c r="B61" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="C61" s="23"/>
-      <c r="D61" s="23"/>
-      <c r="E61" s="23"/>
-      <c r="F61" s="23"/>
-      <c r="G61" s="23"/>
-      <c r="H61" s="23"/>
-      <c r="I61" s="25" t="n">
-        <f aca="false">I58-N(I59)-N(I60)</f>
-        <v>246.98</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="E64" s="22" t="s">
-        <v>73</v>
-      </c>
+      <c r="A60" s="12"/>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="19"/>
+      <c r="E60" s="19"/>
+      <c r="F60" s="19"/>
+      <c r="G60" s="19"/>
+      <c r="H60" s="19"/>
+      <c r="I60" s="21"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="12"/>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="21"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="16"/>
+      <c r="B62" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C62" s="16"/>
+      <c r="D62" s="16"/>
+      <c r="E62" s="16"/>
+      <c r="F62" s="16"/>
+      <c r="G62" s="16"/>
+      <c r="H62" s="16"/>
+      <c r="I62" s="18" t="n">
+        <f aca="false">SUM(I58:I61)</f>
+        <v>24.23</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B64" s="6"/>
+      <c r="C64" s="6"/>
+      <c r="D64" s="6"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="6"/>
+      <c r="I64" s="6"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B68" s="6"/>
-      <c r="C68" s="6"/>
-      <c r="D68" s="6"/>
-      <c r="E68" s="6"/>
-      <c r="F68" s="6"/>
-      <c r="G68" s="6"/>
-      <c r="H68" s="6"/>
-      <c r="I68" s="6"/>
-    </row>
-    <row r="69" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="B69" s="27" t="s">
+      <c r="B65" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C69" s="28" t="s">
+      <c r="I65" s="24" t="n">
+        <f aca="false">I25+I37+I47+I54+I62</f>
+        <v>267.98</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B66" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="D69" s="28"/>
-      <c r="E69" s="28"/>
-      <c r="F69" s="28"/>
-      <c r="G69" s="28"/>
-      <c r="H69" s="28"/>
-      <c r="I69" s="28"/>
-    </row>
-    <row r="70" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="B70" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="C70" s="28" t="s">
+      <c r="I66" s="21"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B67" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="D70" s="28"/>
-      <c r="E70" s="28"/>
-      <c r="F70" s="28"/>
-      <c r="G70" s="28"/>
-      <c r="H70" s="28"/>
-      <c r="I70" s="28"/>
-    </row>
-    <row r="71" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="B71" s="27" t="s">
+      <c r="I67" s="21"/>
+    </row>
+    <row r="68" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="26"/>
+      <c r="B68" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="C71" s="28" t="s">
+      <c r="C68" s="26"/>
+      <c r="D68" s="26"/>
+      <c r="E68" s="26"/>
+      <c r="F68" s="26"/>
+      <c r="G68" s="26"/>
+      <c r="H68" s="26"/>
+      <c r="I68" s="28" t="n">
+        <f aca="false">I65-N(I66)-N(I67)</f>
+        <v>267.98</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="D71" s="28"/>
-      <c r="E71" s="28"/>
-      <c r="F71" s="28"/>
-      <c r="G71" s="28"/>
-      <c r="H71" s="28"/>
-      <c r="I71" s="28"/>
-    </row>
-    <row r="72" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="B72" s="27" t="s">
+      <c r="E71" s="25" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C72" s="28" t="s">
+      <c r="E72" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="D72" s="28"/>
-      <c r="E72" s="28"/>
-      <c r="F72" s="28"/>
-      <c r="G72" s="28"/>
-      <c r="H72" s="28"/>
-      <c r="I72" s="28"/>
-    </row>
-    <row r="73" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="B73" s="27" t="s">
+    </row>
+    <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="C73" s="28" t="s">
-        <v>86</v>
-      </c>
-      <c r="D73" s="28"/>
-      <c r="E73" s="28"/>
-      <c r="F73" s="28"/>
-      <c r="G73" s="28"/>
-      <c r="H73" s="28"/>
-      <c r="I73" s="28"/>
-    </row>
-    <row r="74" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="B74" s="27" t="s">
-        <v>87</v>
-      </c>
-      <c r="C74" s="28" t="s">
-        <v>88</v>
-      </c>
-      <c r="D74" s="28"/>
-      <c r="E74" s="28"/>
-      <c r="F74" s="28"/>
-      <c r="G74" s="28"/>
-      <c r="H74" s="28"/>
-      <c r="I74" s="28"/>
-    </row>
-    <row r="75" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="29" t="s">
-        <v>89</v>
-      </c>
-      <c r="B75" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="C75" s="31" t="s">
-        <v>91</v>
-      </c>
-      <c r="D75" s="31"/>
-      <c r="E75" s="31"/>
-      <c r="F75" s="31"/>
-      <c r="G75" s="31"/>
-      <c r="H75" s="31"/>
-      <c r="I75" s="31"/>
+      <c r="B75" s="6"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="6"/>
+      <c r="E75" s="6"/>
+      <c r="F75" s="6"/>
+      <c r="G75" s="6"/>
+      <c r="H75" s="6"/>
+      <c r="I75" s="6"/>
     </row>
     <row r="76" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="29" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B76" s="30" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C76" s="31" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D76" s="31"/>
       <c r="E76" s="31"/>
@@ -2141,8 +2149,110 @@
       <c r="H76" s="31"/>
       <c r="I76" s="31"/>
     </row>
+    <row r="77" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="B77" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="C77" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="D77" s="31"/>
+      <c r="E77" s="31"/>
+      <c r="F77" s="31"/>
+      <c r="G77" s="31"/>
+      <c r="H77" s="31"/>
+      <c r="I77" s="31"/>
+    </row>
+    <row r="78" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="B78" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C78" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="D78" s="31"/>
+      <c r="E78" s="31"/>
+      <c r="F78" s="31"/>
+      <c r="G78" s="31"/>
+      <c r="H78" s="31"/>
+      <c r="I78" s="31"/>
+    </row>
+    <row r="79" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="B79" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="C79" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="D79" s="31"/>
+      <c r="E79" s="31"/>
+      <c r="F79" s="31"/>
+      <c r="G79" s="31"/>
+      <c r="H79" s="31"/>
+      <c r="I79" s="31"/>
+    </row>
+    <row r="80" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="B80" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="C80" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="D80" s="31"/>
+      <c r="E80" s="31"/>
+      <c r="F80" s="31"/>
+      <c r="G80" s="31"/>
+      <c r="H80" s="31"/>
+      <c r="I80" s="31"/>
+    </row>
+    <row r="81" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="B81" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="C81" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="D81" s="34"/>
+      <c r="E81" s="34"/>
+      <c r="F81" s="34"/>
+      <c r="G81" s="34"/>
+      <c r="H81" s="34"/>
+      <c r="I81" s="34"/>
+    </row>
+    <row r="82" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="B82" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="C82" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="D82" s="34"/>
+      <c r="E82" s="34"/>
+      <c r="F82" s="34"/>
+      <c r="G82" s="34"/>
+      <c r="H82" s="34"/>
+      <c r="I82" s="34"/>
+    </row>
   </sheetData>
-  <mergeCells count="45">
+  <mergeCells count="48">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="B4:E4"/>
@@ -2156,53 +2266,56 @@
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="A13:I13"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="A21:I21"/>
-    <mergeCell ref="D23:H23"/>
-    <mergeCell ref="D24:H24"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="C15:H15"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="A27:I27"/>
     <mergeCell ref="D29:H29"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A42:I42"/>
-    <mergeCell ref="D44:H44"/>
-    <mergeCell ref="D45:H45"/>
-    <mergeCell ref="D46:H46"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D32:H32"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="A39:I39"/>
     <mergeCell ref="A49:I49"/>
     <mergeCell ref="D51:H51"/>
     <mergeCell ref="D52:H52"/>
     <mergeCell ref="D53:H53"/>
-    <mergeCell ref="D54:H54"/>
-    <mergeCell ref="A57:I57"/>
-    <mergeCell ref="A68:I68"/>
-    <mergeCell ref="C69:I69"/>
-    <mergeCell ref="C70:I70"/>
-    <mergeCell ref="C71:I71"/>
-    <mergeCell ref="C72:I72"/>
-    <mergeCell ref="C73:I73"/>
-    <mergeCell ref="C74:I74"/>
-    <mergeCell ref="C75:I75"/>
+    <mergeCell ref="A56:I56"/>
+    <mergeCell ref="D58:H58"/>
+    <mergeCell ref="D59:H59"/>
+    <mergeCell ref="D60:H60"/>
+    <mergeCell ref="D61:H61"/>
+    <mergeCell ref="A64:I64"/>
+    <mergeCell ref="A75:I75"/>
     <mergeCell ref="C76:I76"/>
+    <mergeCell ref="C77:I77"/>
+    <mergeCell ref="C78:I78"/>
+    <mergeCell ref="C79:I79"/>
+    <mergeCell ref="C80:I80"/>
+    <mergeCell ref="C81:I81"/>
+    <mergeCell ref="C82:I82"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C15:C18" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C21:C24" type="list">
       <formula1>'Saetze 2026'!$A$15:$A$17</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B34:B39" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B41:B46" type="list">
       <formula1>'Saetze 2026'!$B$5:$B$7</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C34:C39" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C41:C46" type="list">
       <formula1>'Saetze 2026'!$C$4:$F$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F34:H39" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F41:H46" type="list">
       <formula1>"x"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2234,203 +2347,203 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="32" t="s">
-        <v>94</v>
+      <c r="A1" s="35" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="36" t="n">
+        <v>28</v>
+      </c>
+      <c r="D5" s="36" t="n">
+        <v>14</v>
+      </c>
+      <c r="E5" s="36" t="n">
+        <v>14</v>
+      </c>
+      <c r="F5" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="36" t="s">
         <v>96</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="s">
-        <v>101</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="C5" s="33" t="n">
-        <v>28</v>
-      </c>
-      <c r="D5" s="33" t="n">
-        <v>14</v>
-      </c>
-      <c r="E5" s="33" t="n">
-        <v>14</v>
-      </c>
-      <c r="F5" s="33" t="n">
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="36" t="n">
+        <v>66</v>
+      </c>
+      <c r="D6" s="36" t="n">
+        <v>44</v>
+      </c>
+      <c r="E6" s="36" t="n">
+        <v>44</v>
+      </c>
+      <c r="F6" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="33" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="33" t="n">
-        <v>66</v>
-      </c>
-      <c r="D6" s="33" t="n">
-        <v>44</v>
-      </c>
-      <c r="E6" s="33" t="n">
-        <v>44</v>
-      </c>
-      <c r="F6" s="33" t="n">
+      <c r="G6" s="36" t="n">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="36" t="n">
+        <v>52</v>
+      </c>
+      <c r="D7" s="36" t="n">
+        <v>35</v>
+      </c>
+      <c r="E7" s="36" t="n">
+        <v>35</v>
+      </c>
+      <c r="F7" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="33" t="n">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="B7" s="22" t="s">
-        <v>104</v>
-      </c>
-      <c r="C7" s="33" t="n">
-        <v>52</v>
-      </c>
-      <c r="D7" s="33" t="n">
-        <v>35</v>
-      </c>
-      <c r="E7" s="33" t="n">
-        <v>35</v>
-      </c>
-      <c r="F7" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="33" t="n">
+      <c r="G7" s="36" t="n">
         <v>99</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="B10" s="34" t="n">
+      <c r="A10" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="B10" s="37" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="B11" s="34" t="n">
+      <c r="A11" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="B11" s="37" t="n">
         <v>0.4</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="B12" s="34" t="n">
+      <c r="A12" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="B12" s="37" t="n">
         <v>0.4</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="35" t="n">
+      <c r="A15" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="38" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="C16" s="35" t="n">
+      <c r="A16" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="C16" s="38" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="C17" s="35" t="n">
+      <c r="A17" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="C17" s="38" t="n">
         <v>0.05</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/10_Output/2026-10-21-reisekosten-london-coldewey-holding.xlsx
+++ b/10_Output/2026-10-21-reisekosten-london-coldewey-holding.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Saetze 2026" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Abrechnung!$A$1:$I$83</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Abrechnung!$A$1:$I$87</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -29,7 +29,7 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="C32" authorId="0">
+    <comment ref="C33" authorId="0">
       <text>
         <r>
           <rPr>
@@ -39,18 +39,6 @@
           </rPr>
           <t xml:space="preserve">TfL bucht „Unpaid Fare“ nach, wenn beim Ein- oder Ausstieg nicht korrekt getappt wurde. Ist das eine reine Fahrpreis-Nachzahlung, ist sie absetzbar. Ist es ein Bußgeld (Penalty Fare), ist sie es nicht — dann Zeile löschen.
 Bitte den TfL-Kontoauszug prüfen.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C33" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">OFFEN: „About Town Business Services“ ließ sich nicht eindeutig zuordnen. Wenn das keine Reisekosten waren, Zeile löschen.</t>
         </r>
       </text>
     </comment>
@@ -78,6 +66,18 @@
         </r>
       </text>
     </comment>
+    <comment ref="C36" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">OFFEN: „About Town Business Services“ ließ sich nicht eindeutig zuordnen. Wenn das keine Reisekosten waren, Zeile löschen.</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="C51" authorId="0">
       <text>
         <r>
@@ -86,7 +86,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">OFFEN: Im hochgeladenen Kontoauszug ist für den 06.–08.10. keine Hotelzahlung zu finden. Entweder über ein anderes Konto oder vorab bezahlt.
+          <t xml:space="preserve">OFFEN: Im hochgeladenen Kontoauszug ist für den 06.–07.10. keine Hotelzahlung zu finden. Entweder über ein anderes Konto oder vorab bezahlt.
 Hotelrechnung beilegen und Betrag hier eintragen. Enthält sie Frühstück, den Anteil herausrechnen und oben in Block C das „F“ setzen.</t>
         </r>
       </text>
@@ -126,6 +126,19 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Hier den tatsächlich gezahlten Betrag eintragen.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I67" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Flug Rückreise, 89,98 €. Die Rechnung läuft auf die Coldewey Holding GmbH und die Zahlung steht nicht im privaten Kontoauszug — also hat die Firma direkt gezahlt.
+Hast du den Flug doch privat ausgelegt, diesen Abzug löschen.</t>
         </r>
       </text>
     </comment>
@@ -169,18 +182,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="135">
   <si>
     <t xml:space="preserve">Reisekostenabrechnung</t>
   </si>
   <si>
-    <t xml:space="preserve">London · 07.–08.10.2026 · Sätze siehe Blatt „Saetze 2026“</t>
+    <t xml:space="preserve">London · 06.–07.10.2026 · Sätze siehe Blatt „Saetze 2026“</t>
   </si>
   <si>
     <t xml:space="preserve">Firma</t>
   </si>
   <si>
-    <t xml:space="preserve">Coldewey Holding</t>
+    <t xml:space="preserve">Coldewey Holding GmbH, Im Zuckergarten 28, 55129 Mainz</t>
   </si>
   <si>
     <t xml:space="preserve">Gelb = ausfüllen</t>
@@ -189,7 +202,7 @@
     <t xml:space="preserve">Reisende/r</t>
   </si>
   <si>
-    <t xml:space="preserve">Sascha Coldewey</t>
+    <t xml:space="preserve">Sascha Elimar Coldewey</t>
   </si>
   <si>
     <t xml:space="preserve">Weiß = rechnet sich</t>
@@ -219,13 +232,13 @@
     <t xml:space="preserve">Reise von (Datum, Uhrzeit)</t>
   </si>
   <si>
-    <t xml:space="preserve">07.10.2026, __:__</t>
+    <t xml:space="preserve">06.10.2026, __:__</t>
   </si>
   <si>
     <t xml:space="preserve">Reise bis (Datum, Uhrzeit)</t>
   </si>
   <si>
-    <t xml:space="preserve">08.10.2026, __:__</t>
+    <t xml:space="preserve">07.10.2026, 22:05</t>
   </si>
   <si>
     <t xml:space="preserve">Abrechnung erstellt am</t>
@@ -249,201 +262,216 @@
     <t xml:space="preserve">Zelle I29</t>
   </si>
   <si>
+    <t xml:space="preserve">Flug Hinreise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frankfurt → London am 06.10., gezahlter Preis — die Rückreise ist mit 89,99 € bereits erfasst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zelle I51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel London</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Übernachtung 07. auf 08.10., ohne Frühstücksanteil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A · Fahrt mit eigenem Fahrzeug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Datum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strecke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fahrzeug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kilometer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">€/km</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06.10.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Im Zuckergarten 28 → FRA Terminal 3 und zurück</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pkw, je Kilometer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summe Fahrt eigenes Fahrzeug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B · Fahrtkosten und Transport mit Beleg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Art</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beschreibung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frankfurt → London, Beleg fehlt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07.10.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flug Rückreise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LH 919 London LHR T2 → Frankfurt FRA T1, Rechnung 2026-B2B7-000199110 vom 24.08.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flughafen-Parken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parkhaus FRA Terminal 3, 06.–07.10.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U-Bahn London</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUL Ticket Machine, 7,00 GBP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TfL Nachzahlung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TFL Unpaid Fare, 26,00 GBP — siehe Hinweis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nahverkehr London</t>
+  </si>
+  <si>
+    <t xml:space="preserve">About Town Business Services, 3,15 GBP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">About Town Business Services, 2,00 GBP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summe Fahrtkosten mit Beleg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C · Verpflegungsmehraufwand (Pauschale, kein Beleg nötig)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ort / Land</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abwesenheit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pauschale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kürzung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">London</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An-/Abreisetag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summe Verpflegungsmehraufwand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D · Übernachtung (mit Beleg, ohne Frühstücksanteil)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel / Ort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beleg-Nr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel London, Nacht 06. auf 07.10.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beleg fehlt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summe Übernachtung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E · Sonstige Reisenebenkosten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einreisegenehmigung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UKVI ETA, Pflicht für UK-Einreise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summe sonstige Nebenkosten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ergebnis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summe A bis E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abzüglich Vorschuss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abzüglich direkt von der Firma bezahlt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zu erstatten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_______________________________</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ort, Datum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unterschrift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Offene Punkte und bewusst nicht aufgenommene Positionen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OFFEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frankfurt → London am 06.10. fehlt. Die Opodo-Buchung 25549946153 deckt nur die Rückreise ab (LH 919, 89,99 €). Beleg der Hinreise nachreichen, Block B.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89,98 € laut Rechnung 2026-B2B7-000199110. Rechnungsempfänger ist die Coldewey Holding GmbH mit ihrer USt-ID, und im privaten Kontoauszug ist keine Zahlung an Opodo oder eDreams — die Firma hat also direkt gezahlt. Der Betrag steht deshalb oben in Block B und wird unten wieder abgezogen: er gehört zu den Reisekosten, ist aber keine Auslage von dir. Stimmt das nicht, den Abzug löschen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fehlt im Kopf der Abrechnung. Ohne betrieblichen Anlass ist die Reise nicht absetzbar — Zweck und, wenn möglich, Gesprächspartner eintragen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nacht 06. auf 07.10., Betrag in Block D eintragen. Im Kontoauszug dieses Kontos ist die Zahlung nicht — Rechnung beilegen. Enthält sie Frühstück, den Anteil herausrechnen und in Block C das „F“ setzen, das kürzt die Pauschale um 13,20 €.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Flug</t>
   </si>
   <si>
-    <t xml:space="preserve">Frankfurt → London → Frankfurt, gezahlter Preis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zelle I51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel London</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Übernachtung 07. auf 08.10., ohne Frühstücksanteil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A · Fahrt mit eigenem Fahrzeug</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Datum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strecke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fahrzeug</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kilometer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">€/km</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07.10.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Im Zuckergarten 28 → FRA Terminal 3 und zurück</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pkw, je Kilometer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summe Fahrt eigenes Fahrzeug</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B · Fahrtkosten und Transport mit Beleg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beschreibung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frankfurt → London → Frankfurt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flughafen-Parken</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parkhaus FRA Terminal 3, 07.–08.10.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08.10.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U-Bahn London</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUL Ticket Machine, 7,00 GBP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TfL Nachzahlung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TFL Unpaid Fare, 26,00 GBP — siehe Hinweis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nahverkehr London</t>
-  </si>
-  <si>
-    <t xml:space="preserve">About Town Business Services, 3,15 GBP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">About Town Business Services, 2,00 GBP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summe Fahrtkosten mit Beleg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C · Verpflegungsmehraufwand (Pauschale, kein Beleg nötig)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ort / Land</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abwesenheit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pauschale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kürzung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">London</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An-/Abreisetag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summe Verpflegungsmehraufwand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D · Übernachtung (mit Beleg, ohne Frühstücksanteil)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel / Ort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beleg-Nr.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beleg fehlt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summe Übernachtung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E · Sonstige Reisenebenkosten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06.10.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Einreisegenehmigung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UKVI ETA, Pflicht für UK-Einreise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summe sonstige Nebenkosten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ergebnis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summe A bis E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abzüglich Vorschuss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abzüglich direkt von der Firma bezahlt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zu erstatten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">_______________________________</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ort, Datum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unterschrift</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Offene Punkte und bewusst nicht aufgenommene Positionen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OFFEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reisedatum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Du hast 06. auf 07.10. genannt. Die Kartenumsätze sprechen für 07. auf 08.10.: Abflug Frankfurt „Pier J NonSchengen T3“ am 07.10., Rückflug „WH Smith Heathrow T2“ und Parkhaus-Ausfahrt am 08.10. Die Abrechnung steht auf 07.–08.10. — bitte prüfen.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Betrag in Block D eintragen. Im Kontoauszug dieses Kontos ist die Zahlung nicht — Rechnung beilegen. Enthält sie Frühstück, den Anteil herausrechnen und in Block C das „F“ setzen, das kürzt die Pauschale um 13,20 €.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Betrag in Block B eintragen. Hat die Firma direkt gezahlt, gehört er nicht hierher, sondern unten in „abzüglich direkt von der Firma bezahlt“.</t>
   </si>
   <si>
@@ -459,9 +487,6 @@
     <t xml:space="preserve">3 Buchungen über zusammen 9,81 € nicht eindeutig zuzuordnen. Prüfen.</t>
   </si>
   <si>
-    <t xml:space="preserve">—</t>
-  </si>
-  <si>
     <t xml:space="preserve">UPS-Zoll 14 €</t>
   </si>
   <si>
@@ -472,6 +497,18 @@
   </si>
   <si>
     <t xml:space="preserve">Pret a Manger, Costa, Nazari Food, WH Smith: zusammen 43,74 €. Wird NICHT zusätzlich erstattet, die Verpflegungspauschale deckt das ab. Die Pauschale von 88 € liegt deutlich darüber.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belegdaten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Daten in den Blöcken B und E sind die Kauftage. Im Kontoauszug stehen sie ein bis zwei Tage später, weil der Händler den Kartenumsatz erst dann einreicht. Deshalb sah der Auszug zunächst nach 07.–08.10. aus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vorsteuer Flug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grenzüberschreitende Flüge sind in Deutschland nicht umsatzsteuerpflichtig. Aus den 89,99 € ist keine Vorsteuer zu ziehen, der Betrag wird brutto gebucht.</t>
   </si>
   <si>
     <t xml:space="preserve">Pauschalen 2026</t>
@@ -1172,7 +1209,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
@@ -1547,13 +1584,13 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
@@ -1561,12 +1598,12 @@
       <c r="G30" s="19"/>
       <c r="H30" s="19"/>
       <c r="I30" s="21" t="n">
-        <v>86</v>
+        <v>89.98</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>48</v>
@@ -1580,14 +1617,14 @@
       <c r="G31" s="19"/>
       <c r="H31" s="19"/>
       <c r="I31" s="21" t="n">
-        <v>8.26</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B32" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>50</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -1599,14 +1636,14 @@
       <c r="G32" s="19"/>
       <c r="H32" s="19"/>
       <c r="I32" s="21" t="n">
-        <v>30.68</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="22" t="s">
         <v>52</v>
       </c>
       <c r="C33" s="4" t="s">
@@ -1618,18 +1655,18 @@
       <c r="G33" s="19"/>
       <c r="H33" s="19"/>
       <c r="I33" s="21" t="n">
-        <v>3.73</v>
+        <v>30.68</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D34" s="19"/>
       <c r="E34" s="19"/>
@@ -1637,18 +1674,18 @@
       <c r="G34" s="19"/>
       <c r="H34" s="19"/>
       <c r="I34" s="21" t="n">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D35" s="19"/>
       <c r="E35" s="19"/>
@@ -1656,24 +1693,32 @@
       <c r="G35" s="19"/>
       <c r="H35" s="19"/>
       <c r="I35" s="21" t="n">
-        <v>2.36</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="12"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
+      <c r="A36" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>56</v>
+      </c>
       <c r="D36" s="19"/>
       <c r="E36" s="19"/>
       <c r="F36" s="19"/>
       <c r="G36" s="19"/>
       <c r="H36" s="19"/>
-      <c r="I36" s="21"/>
+      <c r="I36" s="21" t="n">
+        <v>2.36</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="16"/>
       <c r="B37" s="17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C37" s="16"/>
       <c r="D37" s="16"/>
@@ -1683,12 +1728,12 @@
       <c r="H37" s="16"/>
       <c r="I37" s="18" t="n">
         <f aca="false">SUM(I29:I36)</f>
-        <v>134.75</v>
+        <v>224.73</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -1704,25 +1749,25 @@
         <v>32</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I40" s="7" t="s">
         <v>24</v>
@@ -1733,10 +1778,10 @@
         <v>37</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D41" s="15" t="n">
         <f aca="false">IF($A41="","",IFERROR(INDEX('Saetze 2026'!$C$5:$F$7,MATCH($B41,'Saetze 2026'!$B$5:$B$7,0),MATCH($C41,'Saetze 2026'!$C$4:$F$4,0)),0))</f>
@@ -1756,13 +1801,13 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D42" s="15" t="n">
         <f aca="false">IF($A42="","",IFERROR(INDEX('Saetze 2026'!$C$5:$F$7,MATCH($B42,'Saetze 2026'!$B$5:$B$7,0),MATCH($C42,'Saetze 2026'!$C$4:$F$4,0)),0))</f>
@@ -1863,7 +1908,7 @@
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="16"/>
       <c r="B47" s="17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C47" s="16"/>
       <c r="D47" s="16"/>
@@ -1878,7 +1923,7 @@
     </row>
     <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -1894,10 +1939,10 @@
         <v>32</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I50" s="7" t="s">
         <v>24</v>
@@ -1908,10 +1953,10 @@
         <v>37</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D51" s="19"/>
       <c r="E51" s="19"/>
@@ -1945,7 +1990,7 @@
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="16"/>
       <c r="B54" s="17" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C54" s="16"/>
       <c r="D54" s="16"/>
@@ -1960,7 +2005,7 @@
     </row>
     <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -1987,13 +2032,13 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="12" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D58" s="19"/>
       <c r="E58" s="19"/>
@@ -2040,7 +2085,7 @@
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="16"/>
       <c r="B62" s="17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C62" s="16"/>
       <c r="D62" s="16"/>
@@ -2055,7 +2100,7 @@
     </row>
     <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
@@ -2068,29 +2113,31 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I65" s="24" t="n">
         <f aca="false">I25+I37+I47+I54+I62</f>
-        <v>267.98</v>
+        <v>357.96</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="25" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I66" s="21"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="I67" s="21"/>
+        <v>82</v>
+      </c>
+      <c r="I67" s="21" t="n">
+        <v>89.98</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="26"/>
       <c r="B68" s="27" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C68" s="26"/>
       <c r="D68" s="26"/>
@@ -2105,23 +2152,23 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="25" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E71" s="25" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
@@ -2134,13 +2181,13 @@
     </row>
     <row r="76" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="29" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B76" s="30" t="s">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="C76" s="31" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D76" s="31"/>
       <c r="E76" s="31"/>
@@ -2150,31 +2197,31 @@
       <c r="I76" s="31"/>
     </row>
     <row r="77" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="B77" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="C77" s="31" t="s">
+      <c r="A77" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="D77" s="31"/>
-      <c r="E77" s="31"/>
-      <c r="F77" s="31"/>
-      <c r="G77" s="31"/>
-      <c r="H77" s="31"/>
-      <c r="I77" s="31"/>
+      <c r="B77" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="C77" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="D77" s="34"/>
+      <c r="E77" s="34"/>
+      <c r="F77" s="34"/>
+      <c r="G77" s="34"/>
+      <c r="H77" s="34"/>
+      <c r="I77" s="34"/>
     </row>
     <row r="78" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="29" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B78" s="30" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="C78" s="31" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D78" s="31"/>
       <c r="E78" s="31"/>
@@ -2183,15 +2230,15 @@
       <c r="H78" s="31"/>
       <c r="I78" s="31"/>
     </row>
-    <row r="79" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="29" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B79" s="30" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C79" s="31" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D79" s="31"/>
       <c r="E79" s="31"/>
@@ -2200,15 +2247,15 @@
       <c r="H79" s="31"/>
       <c r="I79" s="31"/>
     </row>
-    <row r="80" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="29" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B80" s="30" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C80" s="31" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D80" s="31"/>
       <c r="E80" s="31"/>
@@ -2217,42 +2264,110 @@
       <c r="H80" s="31"/>
       <c r="I80" s="31"/>
     </row>
-    <row r="81" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="32" t="s">
-        <v>96</v>
-      </c>
-      <c r="B81" s="33" t="s">
+    <row r="81" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="B81" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="C81" s="34" t="s">
+      <c r="C81" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="D81" s="34"/>
-      <c r="E81" s="34"/>
-      <c r="F81" s="34"/>
-      <c r="G81" s="34"/>
-      <c r="H81" s="34"/>
-      <c r="I81" s="34"/>
-    </row>
-    <row r="82" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="32" t="s">
-        <v>96</v>
-      </c>
-      <c r="B82" s="33" t="s">
+      <c r="D81" s="31"/>
+      <c r="E81" s="31"/>
+      <c r="F81" s="31"/>
+      <c r="G81" s="31"/>
+      <c r="H81" s="31"/>
+      <c r="I81" s="31"/>
+    </row>
+    <row r="82" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="B82" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="C82" s="34" t="s">
+      <c r="C82" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="D82" s="34"/>
-      <c r="E82" s="34"/>
-      <c r="F82" s="34"/>
-      <c r="G82" s="34"/>
-      <c r="H82" s="34"/>
-      <c r="I82" s="34"/>
+      <c r="D82" s="31"/>
+      <c r="E82" s="31"/>
+      <c r="F82" s="31"/>
+      <c r="G82" s="31"/>
+      <c r="H82" s="31"/>
+      <c r="I82" s="31"/>
+    </row>
+    <row r="83" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="B83" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="C83" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="D83" s="34"/>
+      <c r="E83" s="34"/>
+      <c r="F83" s="34"/>
+      <c r="G83" s="34"/>
+      <c r="H83" s="34"/>
+      <c r="I83" s="34"/>
+    </row>
+    <row r="84" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="B84" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="C84" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="D84" s="34"/>
+      <c r="E84" s="34"/>
+      <c r="F84" s="34"/>
+      <c r="G84" s="34"/>
+      <c r="H84" s="34"/>
+      <c r="I84" s="34"/>
+    </row>
+    <row r="85" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="B85" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="C85" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="D85" s="34"/>
+      <c r="E85" s="34"/>
+      <c r="F85" s="34"/>
+      <c r="G85" s="34"/>
+      <c r="H85" s="34"/>
+      <c r="I85" s="34"/>
+    </row>
+    <row r="86" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="B86" s="33" t="s">
+        <v>107</v>
+      </c>
+      <c r="C86" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="D86" s="34"/>
+      <c r="E86" s="34"/>
+      <c r="F86" s="34"/>
+      <c r="G86" s="34"/>
+      <c r="H86" s="34"/>
+      <c r="I86" s="34"/>
     </row>
   </sheetData>
-  <mergeCells count="48">
+  <mergeCells count="52">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="B4:E4"/>
@@ -2301,6 +2416,10 @@
     <mergeCell ref="C80:I80"/>
     <mergeCell ref="C81:I81"/>
     <mergeCell ref="C82:I82"/>
+    <mergeCell ref="C83:I83"/>
+    <mergeCell ref="C84:I84"/>
+    <mergeCell ref="C85:I85"/>
+    <mergeCell ref="C86:I86"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C21:C24" type="list">
@@ -2348,43 +2467,43 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="35" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C5" s="36" t="n">
         <v>28</v>
@@ -2399,15 +2518,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C6" s="36" t="n">
         <v>66</v>
@@ -2427,10 +2546,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="C7" s="36" t="n">
         <v>52</v>
@@ -2450,12 +2569,12 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B10" s="37" t="n">
         <v>0.2</v>
@@ -2463,7 +2582,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="B11" s="37" t="n">
         <v>0.4</v>
@@ -2471,7 +2590,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="B12" s="37" t="n">
         <v>0.4</v>
@@ -2479,7 +2598,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2492,7 +2611,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="25" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="C16" s="38" t="n">
         <v>0.2</v>
@@ -2500,7 +2619,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C17" s="38" t="n">
         <v>0.05</v>
@@ -2508,42 +2627,42 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/10_Output/2026-10-21-reisekosten-london-coldewey-holding.xlsx
+++ b/10_Output/2026-10-21-reisekosten-london-coldewey-holding.xlsx
@@ -487,10 +487,10 @@
     <t xml:space="preserve">3 Buchungen über zusammen 9,81 € nicht eindeutig zuzuordnen. Prüfen.</t>
   </si>
   <si>
-    <t xml:space="preserve">UPS-Zoll 14 €</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gehört nicht in die Reisekostenabrechnung. Einfuhrabgaben für ein Paket sind eine eigene Betriebsausgabe und werden separat gebucht. Im Kontoauszug nicht enthalten, also wohl bar bezahlt — Beleg aufheben.</t>
+    <t xml:space="preserve">UPS-Einfuhrabgaben</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11,23 €, Paket zugestellt am 26.08.2026 — sechs Wochen vor dieser Reise und ohne Bezug zu ihr. Gehört nicht in die Reisekostenabrechnung, sondern als eigene Betriebsausgabe gebucht, falls die Sendung betrieblich war. Im privaten Kontoauszug ist die Zahlung nicht zu finden.</t>
   </si>
   <si>
     <t xml:space="preserve">Essen in London</t>
